--- a/data/trans_dic/P25A$molestias-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25A$molestias-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, las molestias por causa del tabaco</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, las molestias por causa del tabaco (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,04; 20,14</t>
+          <t>7,71; 19,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,83; 11,68</t>
+          <t>3,94; 11,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,14; 21,95</t>
+          <t>8,81; 21,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,0</t>
+          <t>0,0; 14,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,78</t>
+          <t>0,0; 10,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,82; 26,92</t>
+          <t>7,71; 26,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,79; 15,95</t>
+          <t>6,81; 16,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,54; 9,7</t>
+          <t>3,65; 9,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,77; 20,04</t>
+          <t>10,12; 20,66</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,05; 23,76</t>
+          <t>12,67; 23,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,6; 17,61</t>
+          <t>8,89; 17,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,45; 20,1</t>
+          <t>9,41; 20,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,45; 20,49</t>
+          <t>5,43; 20,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,5; 18,04</t>
+          <t>4,45; 18,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,52; 26,84</t>
+          <t>9,54; 26,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,62; 21,31</t>
+          <t>11,22; 20,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,64; 15,78</t>
+          <t>8,59; 15,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,84; 20,03</t>
+          <t>11,22; 19,94</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,01; 26,71</t>
+          <t>12,8; 26,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,69; 18,43</t>
+          <t>6,55; 17,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,03; 31,35</t>
+          <t>15,88; 30,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,1; 29,0</t>
+          <t>5,17; 27,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 10,99</t>
+          <t>1,72; 12,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 12,89</t>
+          <t>1,45; 12,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,39; 24,2</t>
+          <t>12,65; 23,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,42; 12,96</t>
+          <t>5,5; 13,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,09; 22,54</t>
+          <t>12,32; 23,14</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,74; 31,76</t>
+          <t>18,96; 32,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,78; 16,01</t>
+          <t>6,48; 15,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,93; 18,16</t>
+          <t>7,94; 18,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,34; 31,96</t>
+          <t>13,97; 29,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,23; 23,94</t>
+          <t>8,08; 23,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,38; 22,54</t>
+          <t>9,35; 22,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,29; 28,98</t>
+          <t>19,16; 28,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,84; 16,62</t>
+          <t>8,89; 16,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,25; 18,46</t>
+          <t>10,13; 18,32</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,74; 21,93</t>
+          <t>15,98; 22,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,52; 13,2</t>
+          <t>8,56; 12,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,12; 19,28</t>
+          <t>12,97; 19,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,4; 19,27</t>
+          <t>10,33; 18,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,35; 12,83</t>
+          <t>6,18; 12,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,28; 17,63</t>
+          <t>10,23; 17,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,25; 20,38</t>
+          <t>15,15; 20,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,33; 11,93</t>
+          <t>8,35; 12,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,69; 17,37</t>
+          <t>12,52; 17,33</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, las molestias por causa del tabaco</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, las molestias por causa del tabaco (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10407; 26074</t>
+          <t>9974; 25344</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7233; 22030</t>
+          <t>7426; 22103</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10801; 25944</t>
+          <t>10412; 25825</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 6607</t>
+          <t>0; 5786</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 7052</t>
+          <t>0; 7904</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3670; 14482</t>
+          <t>4147; 14199</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11600; 27229</t>
+          <t>11620; 28467</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9235; 25301</t>
+          <t>9523; 24730</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16808; 34472</t>
+          <t>17411; 35533</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22509; 44393</t>
+          <t>23678; 44441</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21386; 43795</t>
+          <t>22110; 42636</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16747; 35625</t>
+          <t>16680; 35674</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4193; 15761</t>
+          <t>4174; 16104</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4427; 17733</t>
+          <t>4375; 17768</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9085; 23171</t>
+          <t>8238; 22584</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30646; 56210</t>
+          <t>29584; 54496</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29978; 54773</t>
+          <t>29821; 54775</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28575; 52799</t>
+          <t>29567; 52560</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17473; 35869</t>
+          <t>17193; 35733</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11536; 31762</t>
+          <t>11284; 30359</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21400; 41869</t>
+          <t>21202; 41205</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2024; 11508</t>
+          <t>2051; 10943</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1056; 11335</t>
+          <t>1779; 13039</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1074; 9611</t>
+          <t>1082; 9624</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21561; 42097</t>
+          <t>22000; 41505</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14925; 35718</t>
+          <t>15148; 37600</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25151; 46904</t>
+          <t>25647; 48154</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34343; 55265</t>
+          <t>32979; 55870</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13996; 33040</t>
+          <t>13372; 30949</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13996; 32056</t>
+          <t>14009; 33062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13309; 29668</t>
+          <t>12971; 27513</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10428; 27043</t>
+          <t>9133; 26666</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11366; 27293</t>
+          <t>11327; 27569</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51472; 77330</t>
+          <t>51131; 77170</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28235; 53066</t>
+          <t>28377; 52478</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30512; 54923</t>
+          <t>30154; 54524</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>98278; 136992</t>
+          <t>99837; 137503</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>69519; 107720</t>
+          <t>69852; 104258</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>79415; 116761</t>
+          <t>78537; 115709</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26066; 48311</t>
+          <t>25904; 47492</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>24537; 49587</t>
+          <t>23883; 48479</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34529; 59203</t>
+          <t>34350; 59179</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>133501; 178395</t>
+          <t>132571; 176070</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>100155; 143504</t>
+          <t>100440; 145462</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>119428; 163504</t>
+          <t>117851; 163134</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$molestias-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25A$molestias-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,71; 19,58</t>
+          <t>8,06; 19,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,94; 11,72</t>
+          <t>3,94; 11,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,81; 21,85</t>
+          <t>8,99; 22,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,01</t>
+          <t>0,0; 14,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,96</t>
+          <t>0,0; 11,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,71; 26,39</t>
+          <t>6,9; 26,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,81; 16,67</t>
+          <t>6,75; 16,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,65; 9,48</t>
+          <t>3,66; 10,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,12; 20,66</t>
+          <t>10,03; 20,53</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,67; 23,78</t>
+          <t>12,18; 23,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,89; 17,14</t>
+          <t>8,79; 17,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,41; 20,13</t>
+          <t>9,44; 20,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,43; 20,93</t>
+          <t>5,35; 20,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,45; 18,07</t>
+          <t>4,32; 17,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,54; 26,16</t>
+          <t>10,09; 27,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,22; 20,66</t>
+          <t>11,03; 20,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,59; 15,78</t>
+          <t>8,7; 16,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,22; 19,94</t>
+          <t>10,96; 20,08</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,8; 26,61</t>
+          <t>12,33; 26,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,55; 17,61</t>
+          <t>6,98; 17,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,88; 30,86</t>
+          <t>16,32; 31,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,17; 27,58</t>
+          <t>5,09; 27,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 12,64</t>
+          <t>1,48; 11,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 12,91</t>
+          <t>1,49; 13,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,65; 23,86</t>
+          <t>12,73; 24,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,5; 13,65</t>
+          <t>5,23; 13,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,32; 23,14</t>
+          <t>12,18; 22,57</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,96; 32,11</t>
+          <t>19,31; 32,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,48; 15,0</t>
+          <t>6,8; 15,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,94; 18,73</t>
+          <t>8,37; 18,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,97; 29,64</t>
+          <t>14,38; 31,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,08; 23,6</t>
+          <t>9,14; 23,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,35; 22,76</t>
+          <t>9,37; 23,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,16; 28,92</t>
+          <t>19,23; 29,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,89; 16,43</t>
+          <t>8,9; 16,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,13; 18,32</t>
+          <t>10,08; 18,01</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,98; 22,02</t>
+          <t>15,9; 22,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,56; 12,78</t>
+          <t>8,59; 12,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,97; 19,11</t>
+          <t>12,8; 19,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,33; 18,94</t>
+          <t>10,68; 19,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,18; 12,54</t>
+          <t>5,96; 12,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,23; 17,62</t>
+          <t>10,05; 17,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,15; 20,12</t>
+          <t>15,24; 20,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,35; 12,1</t>
+          <t>8,31; 11,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,52; 17,33</t>
+          <t>12,82; 17,48</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9974; 25344</t>
+          <t>10427; 25438</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7426; 22103</t>
+          <t>7430; 22183</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10412; 25825</t>
+          <t>10622; 26461</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5786</t>
+          <t>0; 5806</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 7904</t>
+          <t>0; 8170</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4147; 14199</t>
+          <t>3711; 14113</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11620; 28467</t>
+          <t>11520; 28078</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9523; 24730</t>
+          <t>9541; 26346</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17411; 35533</t>
+          <t>17255; 35317</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23678; 44441</t>
+          <t>22757; 44484</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22110; 42636</t>
+          <t>21851; 44112</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16680; 35674</t>
+          <t>16741; 36364</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4174; 16104</t>
+          <t>4114; 15456</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4375; 17768</t>
+          <t>4243; 17399</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8238; 22584</t>
+          <t>8714; 24130</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29584; 54496</t>
+          <t>29095; 53317</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29821; 54775</t>
+          <t>30183; 55970</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29567; 52560</t>
+          <t>28891; 52932</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17193; 35733</t>
+          <t>16563; 35384</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11284; 30359</t>
+          <t>12030; 30503</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21202; 41205</t>
+          <t>21792; 41557</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2051; 10943</t>
+          <t>2020; 10804</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1779; 13039</t>
+          <t>1522; 11433</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1082; 9624</t>
+          <t>1108; 10008</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22000; 41505</t>
+          <t>22142; 42455</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15148; 37600</t>
+          <t>14405; 37193</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25647; 48154</t>
+          <t>25346; 46976</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32979; 55870</t>
+          <t>33602; 55784</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13372; 30949</t>
+          <t>14037; 32209</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14009; 33062</t>
+          <t>14777; 32452</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12971; 27513</t>
+          <t>13351; 29222</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9133; 26666</t>
+          <t>10325; 26848</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11327; 27569</t>
+          <t>11349; 28481</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51131; 77170</t>
+          <t>51319; 77973</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28377; 52478</t>
+          <t>28415; 51837</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30154; 54524</t>
+          <t>30007; 53595</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>99837; 137503</t>
+          <t>99299; 139156</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>69852; 104258</t>
+          <t>70060; 105400</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>78537; 115709</t>
+          <t>77530; 115363</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25904; 47492</t>
+          <t>26767; 48486</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>23883; 48479</t>
+          <t>23031; 48870</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34350; 59179</t>
+          <t>33752; 58845</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>132571; 176070</t>
+          <t>133355; 177937</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>100440; 145462</t>
+          <t>99887; 144016</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>117851; 163134</t>
+          <t>120630; 164544</t>
         </is>
       </c>
     </row>
